--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9b6af3e2b6c246d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf6344dee0c6b4b9e"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R35e77eb0094e4f9a"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R008452b5c1dc44a9"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf6344dee0c6b4b9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8ac3b313df154ad0"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R008452b5c1dc44a9"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rbc9a9443b4614fe9"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8ac3b313df154ad0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R64c7df79ff9b45f7"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rbc9a9443b4614fe9"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rbf4ce954dc6749ef"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R64c7df79ff9b45f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R64010ee5c1a5479b"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rbf4ce954dc6749ef"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R856fe5e15e444371"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R64010ee5c1a5479b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra42c4f412375462f"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R856fe5e15e444371"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R307ec61b73f44726"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra42c4f412375462f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7a0d5abb26684548"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R307ec61b73f44726"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R601caf6c7e4544ed"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7a0d5abb26684548"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb16fa2cae22d417e"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R601caf6c7e4544ed"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R34934180fa6a4396"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb16fa2cae22d417e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7a1bdd246aa3459b"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R34934180fa6a4396"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R92ac751772064625"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7a1bdd246aa3459b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R16b5b9bb4753489f"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R92ac751772064625"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rc041b67982e14109"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R16b5b9bb4753489f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcd6f382764804181"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rc041b67982e14109"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R23a3a1fd3cf643d6"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcd6f382764804181"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5f72bc6c35134d5f"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R23a3a1fd3cf643d6"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R008500a7da7f439f"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5f72bc6c35134d5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re1489b9d18764dfa"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R008500a7da7f439f"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R1479015eb36a4a52"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re1489b9d18764dfa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0e112a4914894a61"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R1479015eb36a4a52"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R00ea6471bddc4cee"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0e112a4914894a61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6de17663a6b74e3a"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R00ea6471bddc4cee"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R873de74fa8974594"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PivotTableRowOnly/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6de17663a6b74e3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5bfcb0a9a0a343ad"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R873de74fa8974594"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rf8328af98b744a94"/>
   </x:pivotCaches>
 </x:workbook>
 </file>
